--- a/data/exports/optimization/adaptive_weight_tuning_results.xlsx
+++ b/data/exports/optimization/adaptive_weight_tuning_results.xlsx
@@ -503,13 +503,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>0.701</v>
+        <v>0.678</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-05-14 12:50:33</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -559,37 +559,37 @@
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>0.661</v>
+        <v>0.632</v>
       </c>
       <c r="F3" t="n">
-        <v>0.22</v>
+        <v>0.12</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Random</t>
+          <t>Hybrid_50_50</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-05-14 12:50:33</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -601,47 +601,47 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="D4" t="n">
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0.592</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.18</v>
+        <v>0.35</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AntiCrowding</t>
+          <t>Random</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.15</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-05-14 12:50:33</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -657,16 +657,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2.6667</v>
+        <v>2.8667</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6867</v>
+        <v>0.7167</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7778</v>
+        <v>0.2667</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-05-14 12:50:33</t>
+          <t>2026-05-28 19:50:03</t>
         </is>
       </c>
     </row>
@@ -811,28 +811,28 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>0.701</v>
+        <v>0.678</v>
       </c>
       <c r="F2" t="n">
-        <v>0.701</v>
+        <v>0.678</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="J2" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="K2" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -861,28 +861,28 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>0.732</v>
+        <v>0.779</v>
       </c>
       <c r="F3" t="n">
-        <v>0.732</v>
+        <v>0.779</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="J3" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="K3" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="L3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -911,10 +911,10 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>0.667</v>
+        <v>0.71</v>
       </c>
       <c r="F4" t="n">
-        <v>0.667</v>
+        <v>0.71</v>
       </c>
       <c r="G4" t="n">
         <v>4</v>
@@ -923,16 +923,16 @@
         <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="K4" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="L4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -951,7 +951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -961,10 +961,10 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>0.68</v>
+        <v>0.676</v>
       </c>
       <c r="F5" t="n">
-        <v>0.68</v>
+        <v>0.676</v>
       </c>
       <c r="G5" t="n">
         <v>3</v>
@@ -973,16 +973,16 @@
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="J5" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="K5" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1011,16 +1011,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>0.678</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.678</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
         <v>1.64</v>
@@ -1029,10 +1029,10 @@
         <v>1.64</v>
       </c>
       <c r="K6" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="L6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1061,28 +1061,28 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>0.651</v>
+        <v>0.694</v>
       </c>
       <c r="F7" t="n">
-        <v>0.651</v>
+        <v>0.694</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="J7" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="K7" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="L7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1111,16 +1111,16 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>0.637</v>
+        <v>0.618</v>
       </c>
       <c r="F8" t="n">
-        <v>0.661</v>
+        <v>0.632</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
         <v>1.87</v>
@@ -1129,16 +1129,16 @@
         <v>1.85</v>
       </c>
       <c r="K8" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L8" t="n">
         <v>11</v>
       </c>
       <c r="M8" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="N8" t="n">
-        <v>0.22</v>
+        <v>0.12</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1165,34 +1165,34 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>0.63</v>
+        <v>0.613</v>
       </c>
       <c r="F9" t="n">
-        <v>0.652</v>
+        <v>0.627</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="J9" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="K9" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="L9" t="n">
+        <v>10</v>
+      </c>
+      <c r="M9" t="n">
         <v>13</v>
       </c>
-      <c r="M9" t="n">
-        <v>19</v>
-      </c>
       <c r="N9" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1219,34 +1219,34 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>0.612</v>
+        <v>0.61</v>
       </c>
       <c r="F10" t="n">
-        <v>0.635</v>
+        <v>0.632</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="J10" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="K10" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="L10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M10" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="N10" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1273,34 +1273,34 @@
         <v>100</v>
       </c>
       <c r="E11" t="n">
-        <v>0.55</v>
+        <v>0.616</v>
       </c>
       <c r="F11" t="n">
-        <v>0.574</v>
+        <v>0.637</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H11" t="n">
         <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="J11" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="K11" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="L11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="O11" t="n">
         <v>4</v>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1327,34 +1327,34 @@
         <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>0.555</v>
+        <v>0.584</v>
       </c>
       <c r="F12" t="n">
-        <v>0.572</v>
+        <v>0.599</v>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
         <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="J12" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="K12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N12" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="O12" t="n">
         <v>5</v>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1381,34 +1381,34 @@
         <v>100</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.576</v>
       </c>
       <c r="F13" t="n">
-        <v>0.569</v>
+        <v>0.588</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="J13" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="K13" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="L13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="O13" t="n">
         <v>6</v>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1435,34 +1435,34 @@
         <v>100</v>
       </c>
       <c r="E14" t="n">
-        <v>0.535</v>
+        <v>0.521</v>
       </c>
       <c r="F14" t="n">
-        <v>0.592</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
         <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="J14" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="K14" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L14" t="n">
         <v>4</v>
       </c>
       <c r="M14" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="N14" t="n">
-        <v>0.18</v>
+        <v>0.35</v>
       </c>
       <c r="O14" t="n">
         <v>1</v>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1489,10 +1489,10 @@
         <v>100</v>
       </c>
       <c r="E15" t="n">
-        <v>0.521</v>
+        <v>0.535</v>
       </c>
       <c r="F15" t="n">
-        <v>0.57</v>
+        <v>0.587</v>
       </c>
       <c r="G15" t="n">
         <v>3</v>
@@ -1501,22 +1501,22 @@
         <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="J15" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="K15" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M15" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="N15" t="n">
-        <v>0.31</v>
+        <v>0.37</v>
       </c>
       <c r="O15" t="n">
         <v>2</v>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1543,10 +1543,10 @@
         <v>100</v>
       </c>
       <c r="E16" t="n">
-        <v>0.523</v>
+        <v>0.491</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.542</v>
       </c>
       <c r="G16" t="n">
         <v>3</v>
@@ -1555,22 +1555,22 @@
         <v>3</v>
       </c>
       <c r="I16" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="J16" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="K16" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L16" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N16" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1597,10 +1597,10 @@
         <v>100</v>
       </c>
       <c r="E17" t="n">
-        <v>0.482</v>
+        <v>0.521</v>
       </c>
       <c r="F17" t="n">
-        <v>0.54</v>
+        <v>0.573</v>
       </c>
       <c r="G17" t="n">
         <v>3</v>
@@ -1609,22 +1609,22 @@
         <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="J17" t="n">
         <v>1.47</v>
       </c>
       <c r="K17" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M17" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="N17" t="n">
-        <v>0.47</v>
+        <v>0.29</v>
       </c>
       <c r="O17" t="n">
         <v>4</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1651,10 +1651,10 @@
         <v>100</v>
       </c>
       <c r="E18" t="n">
-        <v>0.483</v>
+        <v>0.536</v>
       </c>
       <c r="F18" t="n">
-        <v>0.54</v>
+        <v>0.585</v>
       </c>
       <c r="G18" t="n">
         <v>3</v>
@@ -1663,22 +1663,22 @@
         <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="J18" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="K18" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="L18" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M18" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="N18" t="n">
-        <v>0.41</v>
+        <v>0.3</v>
       </c>
       <c r="O18" t="n">
         <v>5</v>
@@ -1705,10 +1705,10 @@
         <v>100</v>
       </c>
       <c r="E19" t="n">
-        <v>0.504</v>
+        <v>0.51</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="G19" t="n">
         <v>3</v>
@@ -1717,22 +1717,22 @@
         <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="J19" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="K19" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M19" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N19" t="n">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="O19" t="n">
         <v>6</v>
@@ -1756,37 +1756,37 @@
         <v>600</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6683</v>
+        <v>0.71</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6867</v>
+        <v>0.7167</v>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I20" t="n">
-        <v>2.6667</v>
+        <v>2.8667</v>
       </c>
       <c r="J20" t="n">
-        <v>2.6667</v>
+        <v>2.8667</v>
       </c>
       <c r="K20" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="L20" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M20" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N20" t="n">
-        <v>0.7778</v>
+        <v>0.2667</v>
       </c>
       <c r="O20" t="n">
         <v>1</v>
@@ -1810,16 +1810,16 @@
         <v>600</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E21" t="n">
-        <v>0.74</v>
+        <v>0.9367</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7683</v>
+        <v>0.9533</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H21" t="n">
         <v>4</v>
@@ -1828,19 +1828,19 @@
         <v>2.6667</v>
       </c>
       <c r="J21" t="n">
-        <v>2.4444</v>
+        <v>2.6667</v>
       </c>
       <c r="K21" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.7778</v>
+        <v>0.5333</v>
       </c>
       <c r="O21" t="n">
         <v>2</v>
@@ -1864,13 +1864,13 @@
         <v>600</v>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E22" t="n">
-        <v>0.57</v>
+        <v>0.6983</v>
       </c>
       <c r="F22" t="n">
-        <v>0.64</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>3</v>
@@ -1879,22 +1879,22 @@
         <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>2.7778</v>
+        <v>2.5333</v>
       </c>
       <c r="J22" t="n">
-        <v>2.4444</v>
+        <v>2.4667</v>
       </c>
       <c r="K22" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L22" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M22" t="n">
         <v>7</v>
       </c>
       <c r="N22" t="n">
-        <v>0.7778</v>
+        <v>0.4667</v>
       </c>
       <c r="O22" t="n">
         <v>3</v>
@@ -1911,20 +1911,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Weighted_Recent50</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>600</v>
       </c>
       <c r="D23" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.6967</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6367</v>
+        <v>0.7167</v>
       </c>
       <c r="G23" t="n">
         <v>3</v>
@@ -1933,22 +1933,22 @@
         <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>2.5556</v>
+        <v>2.4667</v>
       </c>
       <c r="J23" t="n">
-        <v>2.4444</v>
+        <v>2.4</v>
       </c>
       <c r="K23" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L23" t="n">
+        <v>6</v>
+      </c>
+      <c r="M23" t="n">
         <v>4</v>
       </c>
-      <c r="M23" t="n">
-        <v>8</v>
-      </c>
       <c r="N23" t="n">
-        <v>0.8889</v>
+        <v>0.2667</v>
       </c>
       <c r="O23" t="n">
         <v>4</v>
@@ -1965,20 +1965,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Weighted_Recent50</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>600</v>
       </c>
       <c r="D24" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5417</v>
+        <v>0.7133</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6467000000000001</v>
+        <v>0.7383</v>
       </c>
       <c r="G24" t="n">
         <v>3</v>
@@ -1987,22 +1987,22 @@
         <v>3</v>
       </c>
       <c r="I24" t="n">
-        <v>2.4444</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
-        <v>2.2222</v>
+        <v>2.3333</v>
       </c>
       <c r="K24" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N24" t="n">
-        <v>0.5556</v>
+        <v>0.4667</v>
       </c>
       <c r="O24" t="n">
         <v>5</v>
@@ -2026,13 +2026,13 @@
         <v>600</v>
       </c>
       <c r="D25" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5617</v>
+        <v>0.745</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6183</v>
+        <v>0.7667</v>
       </c>
       <c r="G25" t="n">
         <v>4</v>
@@ -2041,22 +2041,22 @@
         <v>4</v>
       </c>
       <c r="I25" t="n">
+        <v>2.5333</v>
+      </c>
+      <c r="J25" t="n">
         <v>2.3333</v>
       </c>
-      <c r="J25" t="n">
-        <v>2.2222</v>
-      </c>
       <c r="K25" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M25" t="n">
         <v>6</v>
       </c>
       <c r="N25" t="n">
-        <v>0.6667</v>
+        <v>0.4</v>
       </c>
       <c r="O25" t="n">
         <v>6</v>
